--- a/output/pdf_financials_xlsx/GEL.xlsx
+++ b/output/pdf_financials_xlsx/GEL.xlsx
@@ -775,19 +775,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.782443</v>
+        <v>-0.782443</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.279781</v>
+        <v>-2.279781</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1.027711</v>
+        <v>-1.027711</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.203913</v>
+        <v>-1.203913</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.547364</v>
+        <v>-0.547364</v>
       </c>
     </row>
     <row r="17">
@@ -883,19 +883,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.782443</v>
+        <v>-0.782443</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2.279781</v>
+        <v>-2.279781</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.027711</v>
+        <v>-1.027711</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.203913</v>
+        <v>-1.203913</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.547364</v>
+        <v>-0.547364</v>
       </c>
     </row>
     <row r="21">
@@ -949,19 +949,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.782443</v>
+        <v>-0.782443</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2.279781</v>
+        <v>-2.279781</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.027711</v>
+        <v>-1.027711</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.203913</v>
+        <v>-1.203913</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.547364</v>
+        <v>-0.547364</v>
       </c>
     </row>
     <row r="24">
@@ -1067,19 +1067,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.782443</v>
+        <v>-0.782443</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2.279781</v>
+        <v>-2.279781</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1.027711</v>
+        <v>-1.027711</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.203913</v>
+        <v>-1.203913</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.547364</v>
+        <v>-0.547364</v>
       </c>
     </row>
     <row r="28">
@@ -1111,19 +1111,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.782443</v>
+        <v>-0.782443</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>2.279781</v>
+        <v>-2.279781</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.027711</v>
+        <v>-1.027711</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.203913</v>
+        <v>-1.203913</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.547364</v>
+        <v>-0.547364</v>
       </c>
     </row>
     <row r="30">
@@ -1165,19 +1165,19 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -2545,16 +2545,16 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.310039</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.310039</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>2.085904</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.085904</v>
       </c>
     </row>
     <row r="93">
@@ -3985,7 +3985,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -6176,13 +6180,13 @@
         </is>
       </c>
       <c r="G67" s="5" t="n">
-        <v>1.027711</v>
+        <v>-1.027711</v>
       </c>
       <c r="H67" s="5" t="n">
-        <v>1.203913</v>
+        <v>-1.203913</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>0.547364</v>
+        <v>-0.547364</v>
       </c>
     </row>
     <row r="68">
@@ -6896,13 +6900,13 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>0.782443</v>
+        <v>-0.782443</v>
       </c>
       <c r="F85" s="5" t="n">
-        <v>2.279781</v>
+        <v>-2.279781</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>1.027711</v>
+        <v>-1.027711</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/GEL.xlsx
+++ b/output/pdf_financials_xlsx/GEL.xlsx
@@ -690,16 +690,16 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.035489</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.1037</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.071465</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.032047</v>
       </c>
     </row>
     <row r="13">
@@ -1070,16 +1070,16 @@
         <v>-0.782443</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.279781</v>
+        <v>-2.244292</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.027711</v>
+        <v>-0.924011</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.203913</v>
+        <v>-1.132448</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.547364</v>
+        <v>-0.515317</v>
       </c>
     </row>
     <row r="28">
@@ -1114,16 +1114,16 @@
         <v>-0.782443</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.279781</v>
+        <v>-2.244292</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.027711</v>
+        <v>-0.924011</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.203913</v>
+        <v>-1.132448</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.547364</v>
+        <v>-0.515317</v>
       </c>
     </row>
     <row r="30">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">

--- a/output/pdf_financials_xlsx/GEL.xlsx
+++ b/output/pdf_financials_xlsx/GEL.xlsx
@@ -778,10 +778,10 @@
         <v>-0.782443</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-2.279781</v>
+        <v>-2.397783</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-1.027711</v>
+        <v>-1.166429</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>-1.203913</v>
@@ -800,10 +800,10 @@
         <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>0.118002</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>0.138718</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -1070,10 +1070,10 @@
         <v>-0.782443</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.244292</v>
+        <v>-2.362294</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.924011</v>
+        <v>-1.062729</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-1.132448</v>
@@ -1114,10 +1114,10 @@
         <v>-0.782443</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.244292</v>
+        <v>-2.362294</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.924011</v>
+        <v>-1.062729</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-1.132448</v>
@@ -1168,10 +1168,10 @@
         <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>-4.921296047223623</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-0</v>
+        <v>-11.89253696538752</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -1902,10 +1902,10 @@
         <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.003402</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.059263</v>
       </c>
       <c r="F64" s="3" t="n">
         <v>0</v>
@@ -1968,10 +1968,10 @@
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.0215</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.03195</v>
       </c>
       <c r="F67" s="3" t="n">
         <v>0</v>
@@ -5534,7 +5534,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E51" s="5" t="n">
         <v>4.096979</v>
       </c>
@@ -6318,7 +6322,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -6773,7 +6781,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
